--- a/excel/tableau-suivi-vgp.xlsx
+++ b/excel/tableau-suivi-vgp.xlsx
@@ -13,6 +13,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Suivi VGP'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Exemple'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Périodicités'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
@@ -21,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
   <si>
-    <t>Tableau de suivi des VGP</t>
+    <t xml:space="preserve">  Tableau de suivi des VGP</t>
   </si>
   <si>
-    <t>Saisissez le repère, le type et la date de la dernière VGP : la périodicité, l’échéance et le statut se calculent seuls. Mode d’emploi dans l’onglet dédié.</t>
+    <t xml:space="preserve">  Saisissez le repère, le type et la date de la dernière VGP : la périodicité, l’échéance et le statut se calculent seuls. Mode d’emploi dans l’onglet dédié.</t>
   </si>
   <si>
     <t>N°</t>
@@ -325,10 +326,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="&quot;Situation au &quot;dd/mm/yyyy"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -338,8 +340,8 @@
     </font>
     <font>
       <b/>
-      <color rgb="FF12314F"/>
-      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="18"/>
     </font>
     <font>
       <i/>
@@ -352,6 +354,11 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF12314F"/>
+      <sz val="16"/>
     </font>
     <font>
       <b/>
@@ -382,7 +389,7 @@
       <color rgb="FF12805F"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -392,6 +399,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF12314F"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3F7FB"/>
       </patternFill>
     </fill>
     <fill>
@@ -442,39 +454,46 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -483,7 +502,10 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -493,10 +515,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -950,6 +972,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF12314F"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O204"/>
@@ -971,7 +994,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -990,7 +1013,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -1009,10 +1032,14 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <f>"Situation au "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
-      </c>
+        <f>TODAY()</f>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -6463,9 +6490,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:O204"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K204">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -6510,6 +6538,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF12805F"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -6518,87 +6550,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="11" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
-        <f>"Situation au "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
+      <c r="A2" s="12">
+        <f>TODAY()</f>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="14">
         <f>ROWS('Suivi VGP'!$K$5:$K$204)-COUNTIF('Suivi VGP'!$K$5:$K$204,"")</f>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="15">
         <f>COUNTIF('Suivi VGP'!$K$5:$K$204,"En retard")</f>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="16">
         <f>COUNTIF('Suivi VGP'!$K$5:$K$204,"À planifier")</f>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="17">
         <f>COUNTIF('Suivi VGP'!$K$5:$K$204,"À jour")</f>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="16">
         <f>COUNTIF('Suivi VGP'!$K$5:$K$204,"Date à saisir")+COUNTIF('Suivi VGP'!$K$5:$K$204,"Périodicité à confirmer")</f>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="16">
         <f>COUNTIF('Suivi VGP'!$N$5:$N$204,"Oui")</f>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
+      <c r="A10" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="18">
         <f>IFERROR(SMALL('Suivi VGP'!$I$5:$I$204,COUNTIF('Suivi VGP'!$I$5:$I$204,"&lt;"&amp;TODAY())+1),"Aucune")</f>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="12">
+      <c r="B11" s="14">
         <f>IFERROR(INDEX('Suivi VGP'!$B$5:$B$204,MATCH(SMALL('Suivi VGP'!$I$5:$I$204,COUNTIF('Suivi VGP'!$I$5:$I$204,"&lt;"&amp;TODAY())+1),'Suivi VGP'!$I$5:$I$204,0)),"")</f>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="19" t="s">
         <v>25</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
     <oddFooter>&amp;Lmodele-vgp.fr&amp;RPage &amp;P / &amp;N</oddFooter>
   </headerFooter>
@@ -6608,6 +6640,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF9FB0C4"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:O204"/>
@@ -6629,7 +6662,7 @@
     <col min="15" max="15" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="1" ht="36" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6648,7 +6681,7 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -6667,10 +6700,14 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" ht="22" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <f>"Situation au "&amp;TEXT(TODAY(),"dd/mm/yyyy")</f>
-      </c>
+        <f>TODAY()</f>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
     </row>
     <row r="4" ht="32" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
@@ -12173,9 +12210,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:O204"/>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
+    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <conditionalFormatting sqref="K5:K204">
     <cfRule type="expression" dxfId="5" priority="1">
@@ -12220,6 +12258,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -12230,182 +12271,182 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="F1" s="20" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+    <row r="2" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="21">
         <v>6</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="21" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="21" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="4" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="21">
         <v>6</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="5" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C5" s="19">
+      <c r="C5" s="21">
         <v>12</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="21" t="s">
         <v>64</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="21" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+    <row r="6" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="21">
         <v>6</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="21" t="s">
         <v>67</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="21" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+    <row r="7" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="19">
+      <c r="C7" s="21">
         <v>6</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+    <row r="8" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="19" t="s">
+      <c r="F8" s="21" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="19" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:6" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="B9" s="21" t="s">
         <v>63</v>
       </c>
-      <c r="C9" s="19">
+      <c r="C9" s="21">
         <v>12</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="E9" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="21" t="s">
         <v>80</v>
       </c>
     </row>
@@ -12426,12 +12467,19 @@
     <hyperlink ref="F9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="landscape" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;Lmodele-vgp.fr&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF12805F"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:A20"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -12439,102 +12487,102 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="21" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="21" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="21" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="21" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="21" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="21" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="A8" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="22" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="21" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="21" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="21" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="22" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="21" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="23" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+      <c r="A18" s="21" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="21" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="23" t="s">
         <v>99</v>
       </c>
     </row>
@@ -12545,6 +12593,9 @@
     <hyperlink ref="A20" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;Lmodele-vgp.fr&amp;RPage &amp;P / &amp;N</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>